--- a/data/trans_orig/P44C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P44C-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2012</t>
+          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2012 (tasa de respuesta: 98,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>7353</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>12007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>869</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7519</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15346</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>983</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20497</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9555</t>
+          <t>9024</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>14569</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,62 +1336,62 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2984</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1931</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>9920</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2984</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>9815</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9229</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11972</t>
+          <t>11869</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>14684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>62,43%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12637</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>54,57%</t>
         </is>
       </c>
     </row>
@@ -1870,97 +1870,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2230</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4666</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>8,77%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>956</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4562</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5147</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>41,84%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>956</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5031</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>19701</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>7778</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20125</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>12649</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26727</t>
+          <t>27101</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>67,43%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -2439,97 +2439,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2096</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14001</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18764</t>
+          <t>19546</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16710</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28909</t>
+          <t>29142</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14439</t>
+          <t>14436</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>27386</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>41808</t>
+          <t>41183</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>11626</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -3008,97 +3008,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1793</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>7091</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>26,33%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>1912</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>9032</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>8887</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>33,54%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>9117</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16570</t>
+          <t>16307</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,68%</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11595</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24079</t>
+          <t>24097</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,02%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>12556</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>23989</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24415</t>
+          <t>23989</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>70,38%</t>
         </is>
       </c>
     </row>
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>18457</t>
+          <t>19314</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18457</t>
+          <t>19314</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>56,67%</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>973</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>24304</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19215</t>
+          <t>18942</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>38664</t>
+          <t>39232</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>28040</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>47937</t>
+          <t>46870</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>50882</t>
+          <t>50991</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>80114</t>
+          <t>79203</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>50909</t>
+          <t>51277</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>73194</t>
+          <t>74781</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>35849</t>
+          <t>34351</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>56072</t>
+          <t>54953</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>91755</t>
+          <t>91707</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>123938</t>
+          <t>125746</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>24318</t>
+          <t>23998</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12449</t>
+          <t>13238</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>30542</t>
+          <t>29849</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>25889</t>
+          <t>24770</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>48695</t>
+          <t>47511</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2016</t>
+          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2016 (tasa de respuesta: 96,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13667</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12761</t>
+          <t>13883</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19519</t>
+          <t>19157</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23056</t>
+          <t>23057</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19844</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>8919</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>822</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20276</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>12387</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24262</t>
+          <t>23533</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>964</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6122,62 +6122,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2197</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6600</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2197</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6700</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19317</t>
+          <t>18799</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>8548</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19208</t>
+          <t>19206</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21841</t>
+          <t>21730</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,28%</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7986</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15886</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14157</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30556</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>39,99%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21546</t>
+          <t>21548</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34767</t>
+          <t>35223</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13754</t>
+          <t>14127</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>27666</t>
+          <t>28755</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45728</t>
+          <t>46149</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,91%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>17092</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22629</t>
+          <t>22389</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -7225,97 +7225,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1697</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>2119</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1938</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10262</t>
+          <t>10736</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17996</t>
+          <t>17975</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11576</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20228</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14344</t>
+          <t>13539</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24293</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>29211</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42514</t>
+          <t>41908</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -7942,12 +7942,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14994</t>
+          <t>15178</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14994</t>
+          <t>15178</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -8055,12 +8055,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29247</t>
+          <t>29440</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>16479</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>29247</t>
+          <t>29440</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,98%</t>
         </is>
       </c>
     </row>
@@ -8168,12 +8168,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12789</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>26602</t>
+          <t>27838</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -8476,12 +8476,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>22274</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>40448</t>
+          <t>41378</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>23488</t>
+          <t>23819</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>45550</t>
+          <t>45138</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>50402</t>
+          <t>51630</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>79937</t>
+          <t>80105</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>76343</t>
+          <t>74838</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>100789</t>
+          <t>100450</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>45777</t>
+          <t>46453</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>69147</t>
+          <t>69770</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>128399</t>
+          <t>129944</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>163220</t>
+          <t>165528</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>60,2%</t>
         </is>
       </c>
     </row>
@@ -8702,12 +8702,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>22313</t>
+          <t>20940</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>41449</t>
+          <t>42226</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>25669</t>
+          <t>25459</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8752,12 +8752,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>34860</t>
+          <t>34440</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>61035</t>
+          <t>60680</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2023</t>
+          <t>Población según la persona que le recomendó realizarse la prueba de Cáncer de colon en 2023 (tasa de respuesta: 96,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9166,12 +9166,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>12579</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19347</t>
+          <t>19349</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26403</t>
+          <t>26533</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44541</t>
+          <t>44250</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17463</t>
+          <t>17445</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29181</t>
+          <t>29301</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48151</t>
+          <t>48433</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41235</t>
+          <t>40737</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60107</t>
+          <t>59934</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20574</t>
+          <t>20973</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33369</t>
+          <t>33642</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65561</t>
+          <t>66410</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89076</t>
+          <t>88264</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22355</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39917</t>
+          <t>40018</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21446</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37570</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57804</t>
+          <t>57607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -9735,12 +9735,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16095</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -9848,12 +9848,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27986</t>
+          <t>27451</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28818</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46022</t>
+          <t>45635</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>23365</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38624</t>
+          <t>39294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13989</t>
+          <t>14295</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23926</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40480</t>
+          <t>41293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>59736</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>13579</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27450</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>18383</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34656</t>
+          <t>34012</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10309,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10339,62 +10339,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1035</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5118</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3546</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104280</t>
+          <t>103616</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10467,12 +10467,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>100788</t>
+          <t>99778</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -10530,12 +10530,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141592</t>
+          <t>140234</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>318737</t>
+          <t>318798</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10545,12 +10545,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17355</t>
+          <t>17623</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25022</t>
+          <t>25140</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10580,12 +10580,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>179465</t>
+          <t>178596</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>348196</t>
+          <t>344399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -10643,12 +10643,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86811</t>
+          <t>86906</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10693,12 +10693,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83234</t>
+          <t>83382</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>458</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9695</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10958,12 +10958,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29592</t>
+          <t>30583</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49250</t>
+          <t>49774</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20398</t>
+          <t>20687</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32364</t>
+          <t>33560</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54156</t>
+          <t>54588</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78235</t>
+          <t>77660</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11071,12 +11071,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -11099,12 +11099,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76379</t>
+          <t>76837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>97476</t>
+          <t>97479</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29416</t>
+          <t>29290</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>42380</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>110300</t>
+          <t>110137</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>135216</t>
+          <t>135278</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11184,12 +11184,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,33%</t>
         </is>
       </c>
     </row>
@@ -11212,12 +11212,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18524</t>
+          <t>18020</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>33116</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23320</t>
+          <t>23008</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33964</t>
+          <t>33952</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52616</t>
+          <t>52957</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -11447,7 +11447,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>389</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>986</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -11555,12 +11555,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16592</t>
+          <t>15688</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22487</t>
+          <t>22916</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35364</t>
+          <t>36175</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>30620</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47644</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11640,12 +11640,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -11668,12 +11668,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33040</t>
+          <t>33414</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47714</t>
+          <t>47798</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11703,12 +11703,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>50316</t>
+          <t>49410</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>65438</t>
+          <t>63983</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11738,12 +11738,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>87409</t>
+          <t>87988</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>109061</t>
+          <t>108423</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11753,12 +11753,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,78%</t>
         </is>
       </c>
     </row>
@@ -11781,12 +11781,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13919</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25396</t>
+          <t>25446</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>26099</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>42258</t>
+          <t>41961</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -12011,12 +12011,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12081,12 +12081,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>586</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12139,12 +12139,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16569</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28530</t>
+          <t>28741</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12194,12 +12194,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>18029</t>
+          <t>18442</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30914</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12209,12 +12209,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -12237,12 +12237,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>465</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12252,12 +12252,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>64674</t>
+          <t>64957</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>79570</t>
+          <t>79737</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12287,12 +12287,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12307,12 +12307,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>65968</t>
+          <t>65018</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>81772</t>
+          <t>80874</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12322,12 +12322,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -12350,12 +12350,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12365,12 +12365,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12385,12 +12385,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>15936</t>
+          <t>15923</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>27286</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12400,12 +12400,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12420,12 +12420,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>15600</t>
+          <t>15813</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>27946</t>
+          <t>27510</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12435,12 +12435,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -12580,12 +12580,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>30917</t>
+          <t>31680</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12595,12 +12595,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21616</t>
+          <t>21479</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12650,12 +12650,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17316</t>
+          <t>15941</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>47357</t>
+          <t>47442</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>48059</t>
+          <t>54372</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>202738</t>
+          <t>203335</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12708,12 +12708,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>108632</t>
+          <t>107682</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>135525</t>
+          <t>134677</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12743,12 +12743,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12763,12 +12763,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>144400</t>
+          <t>139939</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>325217</t>
+          <t>327345</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12778,12 +12778,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -12806,12 +12806,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>359535</t>
+          <t>360082</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>648162</t>
+          <t>645883</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12821,12 +12821,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12841,12 +12841,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>216768</t>
+          <t>215921</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>248825</t>
+          <t>246153</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>594963</t>
+          <t>593566</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>939211</t>
+          <t>944734</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12891,12 +12891,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,35%</t>
         </is>
       </c>
     </row>
@@ -12919,12 +12919,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>46116</t>
+          <t>44876</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>168866</t>
+          <t>170741</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12934,12 +12934,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>72799</t>
+          <t>73157</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>96851</t>
+          <t>97204</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12969,12 +12969,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12989,12 +12989,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>104436</t>
+          <t>105272</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>251943</t>
+          <t>250474</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13004,12 +13004,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P44C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P44C-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8868</t>
+          <t>9747</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>903</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15611</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>62,5%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14569</t>
+          <t>14973</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9920</t>
+          <t>9475</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>12010</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>14211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6080</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>13074</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>55,58%</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>19694</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>21756</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,51%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12649</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27101</t>
+          <t>27249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12726</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14615</t>
+          <t>14664</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19546</t>
+          <t>19470</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16444</t>
+          <t>16397</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29142</t>
+          <t>28725</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7311</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>27488</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>41183</t>
+          <t>41386</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>11836</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16307</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>46,33%</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>15788</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11658</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24097</t>
+          <t>24225</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,37%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10986</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12190</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>23828</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12190</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>23828</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,91%</t>
         </is>
       </c>
     </row>
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>24304</t>
+          <t>23198</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>39232</t>
+          <t>39901</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>46870</t>
+          <t>48340</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>50991</t>
+          <t>50871</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>79203</t>
+          <t>78365</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>51277</t>
+          <t>51999</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>74781</t>
+          <t>74225</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>34351</t>
+          <t>34129</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>54953</t>
+          <t>56304</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>91707</t>
+          <t>92585</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>125746</t>
+          <t>123878</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,14%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>23487</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13238</t>
+          <t>12790</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>29849</t>
+          <t>30756</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24770</t>
+          <t>26364</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>47511</t>
+          <t>49711</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19157</t>
+          <t>19577</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23057</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14317</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19506</t>
+          <t>19610</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10633</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>20321</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23533</t>
+          <t>23842</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18799</t>
+          <t>19009</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19206</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>9543</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21730</t>
+          <t>22269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11181</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>7497</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15408</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>30068</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21548</t>
+          <t>22206</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>35773</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>3531</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>13720</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28755</t>
+          <t>28713</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46149</t>
+          <t>46038</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,76%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17092</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7809</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22389</t>
+          <t>21896</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>11525</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17975</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>11539</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20346</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>13716</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24084</t>
+          <t>23427</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29211</t>
+          <t>29243</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41908</t>
+          <t>42087</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,46%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -7942,12 +7942,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15178</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15178</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>37,85%</t>
         </is>
       </c>
     </row>
@@ -8055,12 +8055,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>16479</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29440</t>
+          <t>29252</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>16479</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>29440</t>
+          <t>29252</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,5%</t>
         </is>
       </c>
     </row>
@@ -8168,12 +8168,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8183,12 +8183,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8218,12 +8218,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20610</t>
+          <t>20204</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>11878</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>10430</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>27838</t>
+          <t>27079</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -8476,12 +8476,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>20249</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>39915</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>23819</t>
+          <t>22812</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>45138</t>
+          <t>44961</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>51630</t>
+          <t>49838</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>80105</t>
+          <t>80341</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>74838</t>
+          <t>75236</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>100450</t>
+          <t>100180</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>46453</t>
+          <t>46535</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>69770</t>
+          <t>69272</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>129944</t>
+          <t>128458</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>165528</t>
+          <t>164342</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>59,77%</t>
         </is>
       </c>
     </row>
@@ -8702,12 +8702,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>21694</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>42057</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>25459</t>
+          <t>25004</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8752,12 +8752,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>34440</t>
+          <t>33777</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>60680</t>
+          <t>60741</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -9161,32 +9161,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12579</t>
+          <t>14675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9196,32 +9196,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9231,32 +9231,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12158</t>
+          <t>14325</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19349</t>
+          <t>21264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -9274,32 +9274,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35371</t>
+          <t>35268</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26533</t>
+          <t>26258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44250</t>
+          <t>44355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9309,32 +9309,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23136</t>
+          <t>25966</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17445</t>
+          <t>20269</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>32358</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9344,32 +9344,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>58507</t>
+          <t>61235</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48433</t>
+          <t>50294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69738</t>
+          <t>73750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50471</t>
+          <t>56102</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40737</t>
+          <t>45436</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59934</t>
+          <t>65249</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26730</t>
+          <t>29639</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20973</t>
+          <t>22697</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33642</t>
+          <t>36766</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>77201</t>
+          <t>85740</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66410</t>
+          <t>73041</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88264</t>
+          <t>98323</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -9500,102 +9500,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30812</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22677</t>
+          <t>23261</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40018</t>
+          <t>42049</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>17,71%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>32,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>17562</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12231</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24034</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>22,04%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>15,35%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>30,16%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>49687</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>38715</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>60550</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>23,55%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>18,35%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,39%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>15858</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>11144</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>21832</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>22,35%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>15,7%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>30,76%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>46670</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>37262</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>57607</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>23,99%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>19,15%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -9613,17 +9613,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>123568</t>
+          <t>131307</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>123568</t>
+          <t>131307</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123568</t>
+          <t>131307</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9648,17 +9648,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>70968</t>
+          <t>79680</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70968</t>
+          <t>79680</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70968</t>
+          <t>79680</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9683,17 +9683,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>194536</t>
+          <t>210987</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>194536</t>
+          <t>210987</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194536</t>
+          <t>210987</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9730,32 +9730,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12668</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9765,32 +9765,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9800,32 +9800,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -9843,32 +9843,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20656</t>
+          <t>20634</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>13967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27451</t>
+          <t>28118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9878,32 +9878,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15688</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11240</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>21694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9913,32 +9913,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>36344</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28807</t>
+          <t>29393</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45635</t>
+          <t>46972</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30389</t>
+          <t>31530</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23365</t>
+          <t>23570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39294</t>
+          <t>39077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19208</t>
+          <t>23181</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14295</t>
+          <t>18008</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24160</t>
+          <t>29336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>49597</t>
+          <t>54711</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41293</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59736</t>
+          <t>63776</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19899</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13579</t>
+          <t>14200</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>29176</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10493</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>25839</t>
+          <t>27668</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34012</t>
+          <t>35936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -10182,17 +10182,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77170</t>
+          <t>80218</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77170</t>
+          <t>80218</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77170</t>
+          <t>80218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10217,17 +10217,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44972</t>
+          <t>50778</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44972</t>
+          <t>50778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44972</t>
+          <t>50778</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10252,17 +10252,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>122142</t>
+          <t>130996</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122142</t>
+          <t>130996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122142</t>
+          <t>130996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>563</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -10309,12 +10309,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>563</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -10412,32 +10412,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24348</t>
+          <t>24970</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>17815</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>103616</t>
+          <t>33145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10447,32 +10447,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9270</t>
+          <t>10592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10482,32 +10482,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>29910</t>
+          <t>30789</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>99778</t>
+          <t>40546</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -10525,32 +10525,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>282654</t>
+          <t>41923</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140234</t>
+          <t>33546</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>318798</t>
+          <t>50172</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10560,32 +10560,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21467</t>
+          <t>23682</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17623</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25140</t>
+          <t>27683</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10595,32 +10595,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>304121</t>
+          <t>65606</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178596</t>
+          <t>55532</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>344399</t>
+          <t>75602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>61,22%</t>
         </is>
       </c>
     </row>
@@ -10638,32 +10638,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20091</t>
+          <t>21330</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86906</t>
+          <t>29895</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10673,32 +10673,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10708,32 +10708,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>24421</t>
+          <t>26529</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83382</t>
+          <t>35439</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -10751,17 +10751,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>327654</t>
+          <t>88787</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>327654</t>
+          <t>88787</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>327654</t>
+          <t>88787</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10786,17 +10786,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>31359</t>
+          <t>34700</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31359</t>
+          <t>34700</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31359</t>
+          <t>34700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10821,17 +10821,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359013</t>
+          <t>123487</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359013</t>
+          <t>123487</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359013</t>
+          <t>123487</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10868,32 +10868,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>453</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10903,32 +10903,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10938,32 +10938,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>9889</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -10981,32 +10981,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>39435</t>
+          <t>39884</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30583</t>
+          <t>31101</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49774</t>
+          <t>52121</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11016,32 +11016,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>28351</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20687</t>
+          <t>22111</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33560</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11051,32 +11051,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>65539</t>
+          <t>68235</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54588</t>
+          <t>56398</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77660</t>
+          <t>80828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -11094,32 +11094,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87053</t>
+          <t>94200</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76837</t>
+          <t>82054</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>97479</t>
+          <t>105047</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11129,32 +11129,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35935</t>
+          <t>40278</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29290</t>
+          <t>33416</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42380</t>
+          <t>49020</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11164,32 +11164,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>122989</t>
+          <t>134478</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>110137</t>
+          <t>120491</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>135278</t>
+          <t>148263</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,85%</t>
         </is>
       </c>
     </row>
@@ -11207,32 +11207,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>25229</t>
+          <t>30179</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>22388</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33116</t>
+          <t>40107</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11242,32 +11242,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17332</t>
+          <t>18532</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11755</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23008</t>
+          <t>24695</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11277,32 +11277,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>42561</t>
+          <t>48711</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33952</t>
+          <t>38093</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52957</t>
+          <t>60025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -11320,17 +11320,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>154193</t>
+          <t>166646</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>154193</t>
+          <t>166646</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>154193</t>
+          <t>166646</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11355,17 +11355,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>81760</t>
+          <t>89641</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>81760</t>
+          <t>89641</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>81760</t>
+          <t>89641</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11390,17 +11390,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>235953</t>
+          <t>256287</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>235953</t>
+          <t>256287</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>235953</t>
+          <t>256287</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -11447,12 +11447,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11472,32 +11472,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>392</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11507,32 +11507,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -11550,32 +11550,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15688</t>
+          <t>16993</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11585,32 +11585,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28835</t>
+          <t>31179</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22916</t>
+          <t>25043</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36175</t>
+          <t>39427</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11620,32 +11620,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>38157</t>
+          <t>41404</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30620</t>
+          <t>33092</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47963</t>
+          <t>51636</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -11663,32 +11663,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>41433</t>
+          <t>45428</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33414</t>
+          <t>37420</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47798</t>
+          <t>52609</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11698,32 +11698,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>57131</t>
+          <t>63210</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49410</t>
+          <t>55043</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63983</t>
+          <t>71122</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11733,32 +11733,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>98564</t>
+          <t>108638</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>87988</t>
+          <t>97298</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108423</t>
+          <t>119346</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,23%</t>
         </is>
       </c>
     </row>
@@ -11776,32 +11776,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>14995</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20331</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11811,32 +11811,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19416</t>
+          <t>20378</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14112</t>
+          <t>14549</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>25446</t>
+          <t>26865</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11846,32 +11846,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>32993</t>
+          <t>35373</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>26099</t>
+          <t>27637</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>41961</t>
+          <t>44826</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -11889,17 +11889,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>65800</t>
+          <t>72433</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>65800</t>
+          <t>72433</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65800</t>
+          <t>72433</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11924,17 +11924,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>106899</t>
+          <t>116316</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>106899</t>
+          <t>116316</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>106899</t>
+          <t>116316</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11959,17 +11959,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>172699</t>
+          <t>188749</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>172699</t>
+          <t>188749</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>172699</t>
+          <t>188749</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11991,7 +11991,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -12041,32 +12041,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5142</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12076,32 +12076,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>460</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -12119,32 +12119,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>561</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12154,32 +12154,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>22048</t>
+          <t>23234</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>17408</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28741</t>
+          <t>30055</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12189,32 +12189,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>24137</t>
+          <t>25192</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>18442</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>31216</t>
+          <t>32772</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -12232,32 +12232,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12267,32 +12267,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>72040</t>
+          <t>80762</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>64957</t>
+          <t>72074</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>79737</t>
+          <t>88808</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12302,32 +12302,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>73837</t>
+          <t>82652</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>65018</t>
+          <t>73134</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>80874</t>
+          <t>90715</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -12380,32 +12380,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>21240</t>
+          <t>23120</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>15923</t>
+          <t>16807</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27286</t>
+          <t>30402</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12415,32 +12415,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>21240</t>
+          <t>23120</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>27510</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -12458,17 +12458,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12493,17 +12493,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>117483</t>
+          <t>129309</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>117483</t>
+          <t>129309</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>117483</t>
+          <t>129309</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12528,17 +12528,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>121369</t>
+          <t>133158</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>121369</t>
+          <t>133158</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>121369</t>
+          <t>133158</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12575,32 +12575,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>12877</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>28581</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12610,32 +12610,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>16974</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>21479</t>
+          <t>24612</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12645,32 +12645,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>33086</t>
+          <t>36603</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>27363</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>47442</t>
+          <t>48290</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -12688,32 +12688,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>131221</t>
+          <t>132940</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>54372</t>
+          <t>115813</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>203335</t>
+          <t>152502</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12723,32 +12723,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>121373</t>
+          <t>131208</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>107682</t>
+          <t>114704</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>134677</t>
+          <t>146706</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12758,32 +12758,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>252594</t>
+          <t>264148</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>139939</t>
+          <t>239086</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>327345</t>
+          <t>287442</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,54%</t>
         </is>
       </c>
     </row>
@@ -12801,32 +12801,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>493796</t>
+          <t>271075</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>360082</t>
+          <t>248631</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>645883</t>
+          <t>292140</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12836,32 +12836,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>232512</t>
+          <t>260750</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>215921</t>
+          <t>243963</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>246153</t>
+          <t>278028</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12871,32 +12871,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>726308</t>
+          <t>531825</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>593566</t>
+          <t>508378</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>944734</t>
+          <t>562010</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>53,85%</t>
         </is>
       </c>
     </row>
@@ -12914,32 +12914,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>109607</t>
+          <t>119598</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>44876</t>
+          <t>102014</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>170741</t>
+          <t>137463</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12949,32 +12949,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>84116</t>
+          <t>91491</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>73157</t>
+          <t>77970</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>97204</t>
+          <t>105500</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12984,32 +12984,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>193723</t>
+          <t>211088</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>105272</t>
+          <t>189088</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>250474</t>
+          <t>234391</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -13027,17 +13027,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>752270</t>
+          <t>543241</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>752270</t>
+          <t>543241</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>752270</t>
+          <t>543241</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13062,17 +13062,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>453441</t>
+          <t>500423</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>453441</t>
+          <t>500423</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>453441</t>
+          <t>500423</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13097,17 +13097,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1205711</t>
+          <t>1043664</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1205711</t>
+          <t>1043664</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1205711</t>
+          <t>1043664</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
